--- a/MaestraPLU_Panaderia.xlsx
+++ b/MaestraPLU_Panaderia.xlsx
@@ -573,7 +573,7 @@
         <v>22065</v>
       </c>
       <c r="E9" t="str">
-        <v>6990</v>
+        <v>9990</v>
       </c>
       <c r="F9" t="str">
         <v>Por cantidad</v>
@@ -1113,7 +1113,7 @@
         <v>22098</v>
       </c>
       <c r="E36" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F36" t="str">
         <v>Por cantidad</v>
@@ -1133,7 +1133,7 @@
         <v>22018</v>
       </c>
       <c r="E37" t="str">
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="F37" t="str">
         <v>Por cantidad</v>
@@ -1353,7 +1353,7 @@
         <v>22036</v>
       </c>
       <c r="E48" t="str">
-        <v>9490</v>
+        <v>7990</v>
       </c>
       <c r="F48" t="str">
         <v>Por cantidad</v>
@@ -1533,7 +1533,7 @@
         <v>22207</v>
       </c>
       <c r="E57" t="str">
-        <v>6990</v>
+        <v>4990</v>
       </c>
       <c r="F57" t="str">
         <v>Por cantidad</v>
@@ -5713,7 +5713,7 @@
         <v>22292</v>
       </c>
       <c r="E266" t="str">
-        <v>990</v>
+        <v>790</v>
       </c>
       <c r="F266" t="str">
         <v>Por cantidad</v>
@@ -6033,7 +6033,7 @@
         <v>22315</v>
       </c>
       <c r="E282" t="str">
-        <v>990</v>
+        <v>790</v>
       </c>
       <c r="F282" t="str">
         <v>Por cantidad</v>
@@ -6693,7 +6693,7 @@
         <v>20910</v>
       </c>
       <c r="E315" t="str">
-        <v>6990</v>
+        <v>9990</v>
       </c>
       <c r="F315" t="str">
         <v>Por cantidad</v>

--- a/MaestraPLU_Panaderia.xlsx
+++ b/MaestraPLU_Panaderia.xlsx
@@ -964,7 +964,7 @@
         <v>522202</v>
       </c>
       <c r="B29" t="str">
-        <v>TORTA DIA DE LA MADRE 15P FRAMBUESA</v>
+        <v>TORTA DIA DE LA MADRE15P NJA-CHOC</v>
       </c>
       <c r="C29" t="str">
         <v/>

--- a/MaestraPLU_Panaderia.xlsx
+++ b/MaestraPLU_Panaderia.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F341"/>
+  <dimension ref="A1:F342"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7219,9 +7219,29 @@
         <v>Por peso</v>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>524556</v>
+      </c>
+      <c r="B342" t="str">
+        <v>PAN COPIHUE KG</v>
+      </c>
+      <c r="C342" t="str">
+        <v/>
+      </c>
+      <c r="D342" t="str">
+        <v>24556</v>
+      </c>
+      <c r="E342" t="str">
+        <v>3290</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F341"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F342"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/MaestraPLU_Panaderia.xlsx
+++ b/MaestraPLU_Panaderia.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F342"/>
+  <dimension ref="A1:F348"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7221,27 +7221,147 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
+        <v>522545</v>
+      </c>
+      <c r="B342" t="str">
+        <v>TORTA PANQUEQUE NARANJA 15P</v>
+      </c>
+      <c r="C342" t="str">
+        <v/>
+      </c>
+      <c r="D342" t="str">
+        <v>22545</v>
+      </c>
+      <c r="E342" t="str">
+        <v>19990</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>522546</v>
+      </c>
+      <c r="B343" t="str">
+        <v>TORTA PANQUEQUE NARANJA CHOCOLATE 15P</v>
+      </c>
+      <c r="C343" t="str">
+        <v/>
+      </c>
+      <c r="D343" t="str">
+        <v>22546</v>
+      </c>
+      <c r="E343" t="str">
+        <v>19990</v>
+      </c>
+      <c r="F343" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>524547</v>
+      </c>
+      <c r="B344" t="str">
+        <v>TORTA PANQUEQUE CHOCOLATE NUTELLA 15P</v>
+      </c>
+      <c r="C344" t="str">
+        <v/>
+      </c>
+      <c r="D344" t="str">
+        <v>24547</v>
+      </c>
+      <c r="E344" t="str">
+        <v>24990</v>
+      </c>
+      <c r="F344" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>524549</v>
+      </c>
+      <c r="B345" t="str">
+        <v>TORTA PANQUEQUE PISTACHO FRAMB.15P</v>
+      </c>
+      <c r="C345" t="str">
+        <v/>
+      </c>
+      <c r="D345" t="str">
+        <v>24549</v>
+      </c>
+      <c r="E345" t="str">
+        <v>21990</v>
+      </c>
+      <c r="F345" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>524555</v>
+      </c>
+      <c r="B346" t="str">
+        <v>PAN HALLULLA KG</v>
+      </c>
+      <c r="C346" t="str">
+        <v/>
+      </c>
+      <c r="D346" t="str">
+        <v>24555</v>
+      </c>
+      <c r="E346" t="str">
+        <v>2890</v>
+      </c>
+      <c r="F346" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>524557</v>
+      </c>
+      <c r="B347" t="str">
+        <v>PAN MARRAQUETA KG</v>
+      </c>
+      <c r="C347" t="str">
+        <v/>
+      </c>
+      <c r="D347" t="str">
+        <v>24557</v>
+      </c>
+      <c r="E347" t="str">
+        <v>2990</v>
+      </c>
+      <c r="F347" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
         <v>524556</v>
       </c>
-      <c r="B342" t="str">
+      <c r="B348" t="str">
         <v>PAN COPIHUE KG</v>
       </c>
-      <c r="C342" t="str">
-        <v/>
-      </c>
-      <c r="D342" t="str">
+      <c r="C348" t="str">
+        <v/>
+      </c>
+      <c r="D348" t="str">
         <v>24556</v>
       </c>
-      <c r="E342" t="str">
+      <c r="E348" t="str">
         <v>3290</v>
       </c>
-      <c r="F342" t="str">
+      <c r="F348" t="str">
         <v>Por peso</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F342"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F348"/>
   </ignoredErrors>
 </worksheet>
 </file>